--- a/artfynd/A 21240-2023 artfynd.xlsx
+++ b/artfynd/A 21240-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137198019</v>
       </c>
       <c r="B2" t="n">
-        <v>98464</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21240-2023 artfynd.xlsx
+++ b/artfynd/A 21240-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137198019</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21240-2023 artfynd.xlsx
+++ b/artfynd/A 21240-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137198019</v>
       </c>
       <c r="B2" t="n">
-        <v>98477</v>
+        <v>98478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21240-2023 artfynd.xlsx
+++ b/artfynd/A 21240-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137198019</v>
       </c>
       <c r="B2" t="n">
-        <v>98478</v>
+        <v>98483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21240-2023 artfynd.xlsx
+++ b/artfynd/A 21240-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137198019</v>
       </c>
       <c r="B2" t="n">
-        <v>98483</v>
+        <v>98485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21240-2023 artfynd.xlsx
+++ b/artfynd/A 21240-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137198019</v>
       </c>
       <c r="B2" t="n">
-        <v>98485</v>
+        <v>98491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21240-2023 artfynd.xlsx
+++ b/artfynd/A 21240-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137198019</v>
       </c>
       <c r="B2" t="n">
-        <v>98491</v>
+        <v>98503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21240-2023 artfynd.xlsx
+++ b/artfynd/A 21240-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137198019</v>
       </c>
       <c r="B2" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21240-2023 artfynd.xlsx
+++ b/artfynd/A 21240-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137198019</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21240-2023 artfynd.xlsx
+++ b/artfynd/A 21240-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137198019</v>
       </c>
       <c r="B2" t="n">
-        <v>98507</v>
+        <v>98511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
